--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FC483B-93EB-445A-AFCF-7B293B933495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE9AE33-57CF-4795-95C8-E2B93C9449A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="783">
   <si>
     <t>اسم الزيت</t>
   </si>
@@ -3062,7 +3062,7 @@
         <v>14</v>
       </c>
       <c r="C14" s="4">
-        <v>599</v>
+        <v>371</v>
       </c>
       <c r="D14" s="3">
         <v>3</v>
@@ -3232,7 +3232,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="4">
-        <v>753</v>
+        <v>440</v>
       </c>
       <c r="D24" s="3">
         <v>2</v>
@@ -3368,7 +3368,7 @@
         <v>36</v>
       </c>
       <c r="C32" s="4">
-        <v>704</v>
+        <v>534</v>
       </c>
       <c r="D32" s="3">
         <v>1</v>
@@ -3878,7 +3878,7 @@
         <v>60</v>
       </c>
       <c r="C62" s="4">
-        <v>254</v>
+        <v>64</v>
       </c>
       <c r="D62" s="3">
         <v>3</v>
@@ -4167,7 +4167,7 @@
         <v>72</v>
       </c>
       <c r="C79" s="6">
-        <v>505</v>
+        <v>355</v>
       </c>
       <c r="D79" s="5">
         <v>2</v>
@@ -4728,7 +4728,7 @@
         <v>96</v>
       </c>
       <c r="C112" s="4">
-        <v>2523</v>
+        <v>2003</v>
       </c>
       <c r="D112" s="3">
         <v>4</v>
@@ -4847,7 +4847,7 @@
         <v>100</v>
       </c>
       <c r="C119" s="6">
-        <v>1507</v>
+        <v>1198</v>
       </c>
       <c r="D119" s="5">
         <v>6</v>
@@ -5102,13 +5102,13 @@
         <v>534</v>
       </c>
       <c r="C134" s="4">
-        <v>0</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="E134" s="3" t="s">
-        <v>777</v>
+        <v>490</v>
+      </c>
+      <c r="D134" s="3">
+        <v>3</v>
+      </c>
+      <c r="E134" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
@@ -5680,7 +5680,7 @@
         <v>142</v>
       </c>
       <c r="C168" s="4">
-        <v>574</v>
+        <v>14</v>
       </c>
       <c r="D168" s="3">
         <v>5</v>
@@ -5748,7 +5748,7 @@
         <v>146</v>
       </c>
       <c r="C172" s="4">
-        <v>889</v>
+        <v>739</v>
       </c>
       <c r="D172" s="3">
         <v>5</v>
@@ -6139,7 +6139,7 @@
         <v>170</v>
       </c>
       <c r="C195" s="6">
-        <v>213</v>
+        <v>9</v>
       </c>
       <c r="D195" s="5">
         <v>1</v>
@@ -6156,7 +6156,7 @@
         <v>172</v>
       </c>
       <c r="C196" s="4">
-        <v>951</v>
+        <v>648</v>
       </c>
       <c r="D196" s="3">
         <v>4</v>
@@ -6292,7 +6292,7 @@
         <v>182</v>
       </c>
       <c r="C204" s="4">
-        <v>1802</v>
+        <v>1501</v>
       </c>
       <c r="D204" s="3">
         <v>3</v>
@@ -6479,7 +6479,7 @@
         <v>190</v>
       </c>
       <c r="C215" s="6">
-        <v>713</v>
+        <v>345</v>
       </c>
       <c r="D215" s="5">
         <v>5</v>
@@ -6734,7 +6734,7 @@
         <v>204</v>
       </c>
       <c r="C230" s="4">
-        <v>412</v>
+        <v>262</v>
       </c>
       <c r="D230" s="3">
         <v>2</v>
@@ -7822,7 +7822,7 @@
         <v>262</v>
       </c>
       <c r="C294" s="4">
-        <v>1019</v>
+        <v>419</v>
       </c>
       <c r="D294" s="3">
         <v>3</v>
@@ -8043,7 +8043,7 @@
         <v>278</v>
       </c>
       <c r="C307" s="6">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D307" s="5">
         <v>5</v>
@@ -8094,7 +8094,7 @@
         <v>282</v>
       </c>
       <c r="C310" s="4">
-        <v>335</v>
+        <v>5</v>
       </c>
       <c r="D310" s="3">
         <v>2</v>
@@ -8128,7 +8128,7 @@
         <v>286</v>
       </c>
       <c r="C312" s="4">
-        <v>1505</v>
+        <v>1007</v>
       </c>
       <c r="D312" s="3">
         <v>5</v>
@@ -8587,7 +8587,7 @@
         <v>320</v>
       </c>
       <c r="C339" s="6">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="D339" s="5">
         <v>6</v>
@@ -8723,7 +8723,7 @@
         <v>332</v>
       </c>
       <c r="C347" s="6">
-        <v>1506</v>
+        <v>1007</v>
       </c>
       <c r="D347" s="5">
         <v>3</v>
@@ -8808,7 +8808,7 @@
         <v>336</v>
       </c>
       <c r="C352" s="4">
-        <v>1000</v>
+        <v>575</v>
       </c>
       <c r="D352" s="3">
         <v>3</v>
@@ -8995,7 +8995,7 @@
         <v>352</v>
       </c>
       <c r="C363" s="6">
-        <v>325</v>
+        <v>185</v>
       </c>
       <c r="D363" s="5">
         <v>3</v>
@@ -9199,7 +9199,7 @@
         <v>368</v>
       </c>
       <c r="C375" s="6">
-        <v>251</v>
+        <v>12</v>
       </c>
       <c r="D375" s="5">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE9AE33-57CF-4795-95C8-E2B93C9449A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB1E938-558A-4573-9177-E40FD7769DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -2823,6 +2823,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CDFDB80-1D2C-45C3-A7F3-426073D2B576}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E387"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3181,7 +3184,7 @@
         <v>402</v>
       </c>
       <c r="C21" s="6">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="D21" s="5">
         <v>2</v>
@@ -5102,7 +5105,7 @@
         <v>534</v>
       </c>
       <c r="C134" s="4">
-        <v>490</v>
+        <v>168</v>
       </c>
       <c r="D134" s="3">
         <v>3</v>
@@ -6156,7 +6159,7 @@
         <v>172</v>
       </c>
       <c r="C196" s="4">
-        <v>648</v>
+        <v>318</v>
       </c>
       <c r="D196" s="3">
         <v>4</v>
@@ -6547,7 +6550,7 @@
         <v>194</v>
       </c>
       <c r="C219" s="6">
-        <v>755</v>
+        <v>310</v>
       </c>
       <c r="D219" s="5">
         <v>5</v>
@@ -8128,7 +8131,7 @@
         <v>286</v>
       </c>
       <c r="C312" s="4">
-        <v>1007</v>
+        <v>607</v>
       </c>
       <c r="D312" s="3">
         <v>5</v>
@@ -9414,5 +9417,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB1E938-558A-4573-9177-E40FD7769DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65419099-5BE8-458B-89ED-F118F94EA767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -3490,7 +3490,7 @@
         <v>414</v>
       </c>
       <c r="C39" s="6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>777</v>
@@ -4323,7 +4323,7 @@
         <v>474</v>
       </c>
       <c r="C88" s="4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>777</v>
@@ -4544,7 +4544,7 @@
         <v>88</v>
       </c>
       <c r="C101" s="6">
-        <v>602</v>
+        <v>764</v>
       </c>
       <c r="D101" s="5">
         <v>1</v>
@@ -6057,7 +6057,7 @@
         <v>164</v>
       </c>
       <c r="C190" s="4">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="D190" s="3">
         <v>3</v>
@@ -6550,7 +6550,7 @@
         <v>194</v>
       </c>
       <c r="C219" s="6">
-        <v>310</v>
+        <v>410</v>
       </c>
       <c r="D219" s="5">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65419099-5BE8-458B-89ED-F118F94EA767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6735F0B-F136-4146-9F90-0D047D196113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="783">
   <si>
     <t>اسم الزيت</t>
   </si>
@@ -3490,13 +3490,13 @@
         <v>414</v>
       </c>
       <c r="C39" s="6">
-        <v>1000</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>777</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>777</v>
+        <v>0</v>
+      </c>
+      <c r="D39" s="5">
+        <v>3</v>
+      </c>
+      <c r="E39" s="5">
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -4325,11 +4325,11 @@
       <c r="C88" s="4">
         <v>1000</v>
       </c>
-      <c r="D88" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>777</v>
+      <c r="D88" s="3">
+        <v>2</v>
+      </c>
+      <c r="E88" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
@@ -4547,7 +4547,7 @@
         <v>764</v>
       </c>
       <c r="D101" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E101" s="5">
         <v>4</v>
@@ -5105,7 +5105,7 @@
         <v>534</v>
       </c>
       <c r="C134" s="4">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="D134" s="3">
         <v>3</v>
@@ -5683,7 +5683,7 @@
         <v>142</v>
       </c>
       <c r="C168" s="4">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D168" s="3">
         <v>5</v>
@@ -6063,7 +6063,7 @@
         <v>3</v>
       </c>
       <c r="E190" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.35">
@@ -6091,7 +6091,7 @@
         <v>600</v>
       </c>
       <c r="C192" s="4">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>777</v>
@@ -6210,7 +6210,7 @@
         <v>174</v>
       </c>
       <c r="C199" s="6">
-        <v>535</v>
+        <v>235</v>
       </c>
       <c r="D199" s="5">
         <v>3</v>
@@ -7264,7 +7264,7 @@
         <v>230</v>
       </c>
       <c r="C261" s="6">
-        <v>826</v>
+        <v>542</v>
       </c>
       <c r="D261" s="5">
         <v>3</v>
@@ -7451,7 +7451,7 @@
         <v>242</v>
       </c>
       <c r="C272" s="4">
-        <v>245</v>
+        <v>109</v>
       </c>
       <c r="D272" s="3">
         <v>3</v>
@@ -7604,7 +7604,7 @@
         <v>252</v>
       </c>
       <c r="C281" s="6">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="D281" s="5">
         <v>6</v>
@@ -7689,7 +7689,7 @@
         <v>258</v>
       </c>
       <c r="C286" s="4">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="D286" s="3">
         <v>4</v>
@@ -8250,7 +8250,7 @@
         <v>296</v>
       </c>
       <c r="C319" s="6">
-        <v>610</v>
+        <v>417</v>
       </c>
       <c r="D319" s="5">
         <v>5</v>
@@ -8811,7 +8811,7 @@
         <v>336</v>
       </c>
       <c r="C352" s="4">
-        <v>575</v>
+        <v>212</v>
       </c>
       <c r="D352" s="3">
         <v>3</v>
@@ -9015,7 +9015,7 @@
         <v>354</v>
       </c>
       <c r="C364" s="4">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D364" s="3">
         <v>4</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6735F0B-F136-4146-9F90-0D047D196113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9659BB-172D-4C9B-A701-D50DA35D3173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="783">
   <si>
     <t>اسم الزيت</t>
   </si>
@@ -3320,7 +3320,7 @@
         <v>32</v>
       </c>
       <c r="C29" s="6">
-        <v>1099</v>
+        <v>899</v>
       </c>
       <c r="D29" s="5">
         <v>3</v>
@@ -4544,7 +4544,7 @@
         <v>88</v>
       </c>
       <c r="C101" s="6">
-        <v>764</v>
+        <v>564</v>
       </c>
       <c r="D101" s="5">
         <v>3</v>
@@ -6093,11 +6093,11 @@
       <c r="C192" s="4">
         <v>500</v>
       </c>
-      <c r="D192" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="E192" s="3" t="s">
-        <v>777</v>
+      <c r="D192" s="3">
+        <v>3</v>
+      </c>
+      <c r="E192" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.35">
@@ -8063,7 +8063,7 @@
         <v>280</v>
       </c>
       <c r="C308" s="4">
-        <v>600</v>
+        <v>389</v>
       </c>
       <c r="D308" s="3">
         <v>6</v>
@@ -8505,7 +8505,7 @@
         <v>312</v>
       </c>
       <c r="C334" s="4">
-        <v>1119</v>
+        <v>859</v>
       </c>
       <c r="D334" s="3" t="s">
         <v>779</v>
@@ -8556,7 +8556,7 @@
         <v>738</v>
       </c>
       <c r="C337" s="6">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="D337" s="5" t="s">
         <v>779</v>
@@ -8573,7 +8573,7 @@
         <v>318</v>
       </c>
       <c r="C338" s="4">
-        <v>2330</v>
+        <v>1630</v>
       </c>
       <c r="D338" s="3" t="s">
         <v>779</v>
@@ -8607,7 +8607,7 @@
         <v>322</v>
       </c>
       <c r="C340" s="4">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="D340" s="3" t="s">
         <v>779</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9659BB-172D-4C9B-A701-D50DA35D3173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52FB9223-0683-42D5-B77E-AD8BDEC6E718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="783">
   <si>
     <t>اسم الزيت</t>
   </si>
@@ -3779,13 +3779,13 @@
         <v>436</v>
       </c>
       <c r="C56" s="4">
-        <v>0</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>777</v>
+        <v>1000</v>
+      </c>
+      <c r="D56" s="3">
+        <v>5</v>
+      </c>
+      <c r="E56" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
@@ -4034,13 +4034,13 @@
         <v>456</v>
       </c>
       <c r="C71" s="6">
-        <v>0</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>777</v>
+        <v>847</v>
+      </c>
+      <c r="D71" s="5">
+        <v>2</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
@@ -4493,13 +4493,13 @@
         <v>492</v>
       </c>
       <c r="C98" s="4">
-        <v>0</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>777</v>
+        <v>1000</v>
+      </c>
+      <c r="D98" s="3">
+        <v>3</v>
+      </c>
+      <c r="E98" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
@@ -4799,13 +4799,13 @@
         <v>516</v>
       </c>
       <c r="C116" s="4">
-        <v>0</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>777</v>
+        <v>1000</v>
+      </c>
+      <c r="D116" s="3">
+        <v>2</v>
+      </c>
+      <c r="E116" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
@@ -5105,7 +5105,7 @@
         <v>534</v>
       </c>
       <c r="C134" s="4">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="D134" s="3">
         <v>3</v>
@@ -5683,7 +5683,7 @@
         <v>142</v>
       </c>
       <c r="C168" s="4">
-        <v>0</v>
+        <v>596</v>
       </c>
       <c r="D168" s="3">
         <v>5</v>
@@ -6097,7 +6097,7 @@
         <v>3</v>
       </c>
       <c r="E192" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.35">
@@ -6346,13 +6346,13 @@
         <v>612</v>
       </c>
       <c r="C207" s="6">
-        <v>0</v>
-      </c>
-      <c r="D207" s="5" t="s">
-        <v>777</v>
-      </c>
-      <c r="E207" s="5" t="s">
-        <v>777</v>
+        <v>1000</v>
+      </c>
+      <c r="D207" s="5">
+        <v>5</v>
+      </c>
+      <c r="E207" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.35">
@@ -6601,13 +6601,13 @@
         <v>628</v>
       </c>
       <c r="C222" s="4">
-        <v>0</v>
-      </c>
-      <c r="D222" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="E222" s="3" t="s">
-        <v>777</v>
+        <v>738</v>
+      </c>
+      <c r="D222" s="3">
+        <v>4</v>
+      </c>
+      <c r="E222" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.35">
@@ -6686,7 +6686,7 @@
         <v>200</v>
       </c>
       <c r="C227" s="6">
-        <v>616</v>
+        <v>1616</v>
       </c>
       <c r="D227" s="5">
         <v>1</v>
@@ -7944,13 +7944,13 @@
         <v>712</v>
       </c>
       <c r="C301" s="6">
-        <v>0</v>
-      </c>
-      <c r="D301" s="5" t="s">
-        <v>777</v>
-      </c>
-      <c r="E301" s="5" t="s">
-        <v>777</v>
+        <v>1000</v>
+      </c>
+      <c r="D301" s="5">
+        <v>2</v>
+      </c>
+      <c r="E301" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.35">
@@ -8369,13 +8369,13 @@
         <v>732</v>
       </c>
       <c r="C326" s="4">
-        <v>0</v>
-      </c>
-      <c r="D326" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="E326" s="3" t="s">
-        <v>777</v>
+        <v>675</v>
+      </c>
+      <c r="D326" s="3">
+        <v>4</v>
+      </c>
+      <c r="E326" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.35">
@@ -8828,7 +8828,7 @@
         <v>338</v>
       </c>
       <c r="C353" s="6">
-        <v>766</v>
+        <v>1766</v>
       </c>
       <c r="D353" s="5">
         <v>1</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52FB9223-0683-42D5-B77E-AD8BDEC6E718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8BD28FE-12D3-4CB9-9C6C-D42061B399DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -7111,7 +7111,7 @@
         <v>666</v>
       </c>
       <c r="C252" s="4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D252" s="3" t="s">
         <v>777</v>
@@ -8607,7 +8607,7 @@
         <v>322</v>
       </c>
       <c r="C340" s="4">
-        <v>19</v>
+        <v>184</v>
       </c>
       <c r="D340" s="3" t="s">
         <v>779</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8BD28FE-12D3-4CB9-9C6C-D42061B399DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9F611B-641E-46B2-9E29-0A3433D61572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -3235,7 +3235,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="4">
-        <v>440</v>
+        <v>290</v>
       </c>
       <c r="D24" s="3">
         <v>2</v>
@@ -3949,7 +3949,7 @@
         <v>64</v>
       </c>
       <c r="C66" s="4">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="D66" s="3">
         <v>3</v>
@@ -4918,7 +4918,7 @@
         <v>106</v>
       </c>
       <c r="C123" s="6">
-        <v>692</v>
+        <v>542</v>
       </c>
       <c r="D123" s="5">
         <v>5</v>
@@ -6057,7 +6057,7 @@
         <v>164</v>
       </c>
       <c r="C190" s="4">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="D190" s="3">
         <v>3</v>
@@ -6550,7 +6550,7 @@
         <v>194</v>
       </c>
       <c r="C219" s="6">
-        <v>410</v>
+        <v>610</v>
       </c>
       <c r="D219" s="5">
         <v>5</v>
@@ -7604,7 +7604,7 @@
         <v>252</v>
       </c>
       <c r="C281" s="6">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="D281" s="5">
         <v>6</v>
@@ -8216,7 +8216,7 @@
         <v>292</v>
       </c>
       <c r="C317" s="6">
-        <v>1073</v>
+        <v>923</v>
       </c>
       <c r="D317" s="5">
         <v>6</v>
@@ -8505,7 +8505,7 @@
         <v>312</v>
       </c>
       <c r="C334" s="4">
-        <v>859</v>
+        <v>709</v>
       </c>
       <c r="D334" s="3" t="s">
         <v>779</v>
@@ -8811,7 +8811,7 @@
         <v>336</v>
       </c>
       <c r="C352" s="4">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="D352" s="3">
         <v>3</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9F611B-641E-46B2-9E29-0A3433D61572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A77C2F9-5F98-4A45-AC9B-01AB2542CC23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2980,7 +2980,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="6">
-        <v>1217</v>
+        <v>1067</v>
       </c>
       <c r="D9" s="5">
         <v>3</v>
@@ -3388,7 +3388,7 @@
         <v>38</v>
       </c>
       <c r="C33" s="6">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="D33" s="5">
         <v>2</v>
@@ -4187,7 +4187,7 @@
         <v>74</v>
       </c>
       <c r="C80" s="4">
-        <v>659</v>
+        <v>359</v>
       </c>
       <c r="D80" s="3">
         <v>4</v>
@@ -4289,7 +4289,7 @@
         <v>80</v>
       </c>
       <c r="C86" s="4">
-        <v>2029</v>
+        <v>1665</v>
       </c>
       <c r="D86" s="3">
         <v>3</v>
@@ -4323,7 +4323,7 @@
         <v>474</v>
       </c>
       <c r="C88" s="4">
-        <v>1000</v>
+        <v>635</v>
       </c>
       <c r="D88" s="3">
         <v>2</v>
@@ -4850,7 +4850,7 @@
         <v>100</v>
       </c>
       <c r="C119" s="6">
-        <v>1198</v>
+        <v>948</v>
       </c>
       <c r="D119" s="5">
         <v>6</v>
@@ -5105,7 +5105,7 @@
         <v>534</v>
       </c>
       <c r="C134" s="4">
-        <v>76</v>
+        <v>776</v>
       </c>
       <c r="D134" s="3">
         <v>3</v>
@@ -5445,7 +5445,7 @@
         <v>128</v>
       </c>
       <c r="C154" s="4">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D154" s="3">
         <v>6</v>
@@ -5462,7 +5462,7 @@
         <v>130</v>
       </c>
       <c r="C155" s="6">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="D155" s="5">
         <v>2</v>
@@ -6057,7 +6057,7 @@
         <v>164</v>
       </c>
       <c r="C190" s="4">
-        <v>1200</v>
+        <v>3200</v>
       </c>
       <c r="D190" s="3">
         <v>3</v>
@@ -6091,7 +6091,7 @@
         <v>600</v>
       </c>
       <c r="C192" s="4">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="D192" s="3">
         <v>3</v>
@@ -6295,7 +6295,7 @@
         <v>182</v>
       </c>
       <c r="C204" s="4">
-        <v>1501</v>
+        <v>1351</v>
       </c>
       <c r="D204" s="3">
         <v>3</v>
@@ -6788,7 +6788,7 @@
         <v>642</v>
       </c>
       <c r="C233" s="6">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="D233" s="5" t="s">
         <v>777</v>
@@ -6975,7 +6975,7 @@
         <v>212</v>
       </c>
       <c r="C244" s="4">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="D244" s="3">
         <v>5</v>
@@ -7298,7 +7298,7 @@
         <v>234</v>
       </c>
       <c r="C263" s="6">
-        <v>608</v>
+        <v>458</v>
       </c>
       <c r="D263" s="5">
         <v>3</v>
@@ -7604,7 +7604,7 @@
         <v>252</v>
       </c>
       <c r="C281" s="6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D281" s="5">
         <v>6</v>
@@ -8216,7 +8216,7 @@
         <v>292</v>
       </c>
       <c r="C317" s="6">
-        <v>923</v>
+        <v>602</v>
       </c>
       <c r="D317" s="5">
         <v>6</v>
@@ -8250,7 +8250,7 @@
         <v>296</v>
       </c>
       <c r="C319" s="6">
-        <v>417</v>
+        <v>315</v>
       </c>
       <c r="D319" s="5">
         <v>5</v>
@@ -9168,7 +9168,7 @@
         <v>366</v>
       </c>
       <c r="C373" s="6">
-        <v>290</v>
+        <v>90</v>
       </c>
       <c r="D373" s="5" t="s">
         <v>779</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A77C2F9-5F98-4A45-AC9B-01AB2542CC23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F574DB-22B9-4F62-8656-0F243E5363A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -4187,7 +4187,7 @@
         <v>74</v>
       </c>
       <c r="C80" s="4">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="D80" s="3">
         <v>4</v>
@@ -5683,7 +5683,7 @@
         <v>142</v>
       </c>
       <c r="C168" s="4">
-        <v>596</v>
+        <v>316</v>
       </c>
       <c r="D168" s="3">
         <v>5</v>
@@ -6295,7 +6295,7 @@
         <v>182</v>
       </c>
       <c r="C204" s="4">
-        <v>1351</v>
+        <v>985</v>
       </c>
       <c r="D204" s="3">
         <v>3</v>
@@ -8216,7 +8216,7 @@
         <v>292</v>
       </c>
       <c r="C317" s="6">
-        <v>602</v>
+        <v>302</v>
       </c>
       <c r="D317" s="5">
         <v>6</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F574DB-22B9-4F62-8656-0F243E5363A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAB37FA-F8FD-4A5A-94C5-7587D61F33A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -4714,7 +4714,7 @@
         <v>94</v>
       </c>
       <c r="C111" s="6">
-        <v>737</v>
+        <v>0</v>
       </c>
       <c r="D111" s="5">
         <v>2</v>
@@ -6057,7 +6057,7 @@
         <v>164</v>
       </c>
       <c r="C190" s="4">
-        <v>3200</v>
+        <v>3100</v>
       </c>
       <c r="D190" s="3">
         <v>3</v>
@@ -6601,7 +6601,7 @@
         <v>628</v>
       </c>
       <c r="C222" s="4">
-        <v>738</v>
+        <v>638</v>
       </c>
       <c r="D222" s="3">
         <v>4</v>
@@ -6720,7 +6720,7 @@
         <v>202</v>
       </c>
       <c r="C229" s="6">
-        <v>2270</v>
+        <v>2052</v>
       </c>
       <c r="D229" s="5">
         <v>4</v>
@@ -7502,7 +7502,7 @@
         <v>246</v>
       </c>
       <c r="C275" s="6">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="D275" s="5">
         <v>3</v>
@@ -7689,7 +7689,7 @@
         <v>258</v>
       </c>
       <c r="C286" s="4">
-        <v>234</v>
+        <v>754</v>
       </c>
       <c r="D286" s="3">
         <v>4</v>
@@ -8012,7 +8012,7 @@
         <v>276</v>
       </c>
       <c r="C305" s="6">
-        <v>480</v>
+        <v>280</v>
       </c>
       <c r="D305" s="5">
         <v>2</v>
@@ -8352,7 +8352,7 @@
         <v>300</v>
       </c>
       <c r="C325" s="6">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="D325" s="5">
         <v>3</v>
@@ -9287,7 +9287,7 @@
         <v>372</v>
       </c>
       <c r="C380" s="4">
-        <v>2256</v>
+        <v>2013</v>
       </c>
       <c r="D380" s="3">
         <v>1</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAB37FA-F8FD-4A5A-94C5-7587D61F33A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2F12D0-8411-474E-9E77-1526F2491BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4187,7 +4187,7 @@
         <v>74</v>
       </c>
       <c r="C80" s="4">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="D80" s="3">
         <v>4</v>
@@ -6754,7 +6754,7 @@
         <v>638</v>
       </c>
       <c r="C231" s="6">
-        <v>0</v>
+        <v>1013</v>
       </c>
       <c r="D231" s="5" t="s">
         <v>777</v>
@@ -8573,7 +8573,7 @@
         <v>318</v>
       </c>
       <c r="C338" s="4">
-        <v>1630</v>
+        <v>6216</v>
       </c>
       <c r="D338" s="3" t="s">
         <v>779</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2F12D0-8411-474E-9E77-1526F2491BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53AAF42-5F9E-450C-B860-F6065E1FF9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -2980,7 +2980,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="6">
-        <v>1067</v>
+        <v>3067</v>
       </c>
       <c r="D9" s="5">
         <v>3</v>
@@ -3235,7 +3235,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="4">
-        <v>290</v>
+        <v>1290</v>
       </c>
       <c r="D24" s="3">
         <v>2</v>
@@ -3490,7 +3490,7 @@
         <v>414</v>
       </c>
       <c r="C39" s="6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D39" s="5">
         <v>3</v>
@@ -4068,7 +4068,7 @@
         <v>458</v>
       </c>
       <c r="C73" s="6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>777</v>
@@ -4255,7 +4255,7 @@
         <v>76</v>
       </c>
       <c r="C84" s="4">
-        <v>383</v>
+        <v>1383</v>
       </c>
       <c r="D84" s="3">
         <v>3</v>
@@ -4289,7 +4289,7 @@
         <v>80</v>
       </c>
       <c r="C86" s="4">
-        <v>1665</v>
+        <v>2665</v>
       </c>
       <c r="D86" s="3">
         <v>3</v>
@@ -4935,7 +4935,7 @@
         <v>522</v>
       </c>
       <c r="C124" s="4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>777</v>
@@ -5547,7 +5547,7 @@
         <v>134</v>
       </c>
       <c r="C160" s="4">
-        <v>676</v>
+        <v>1676</v>
       </c>
       <c r="D160" s="3">
         <v>1</v>
@@ -5717,7 +5717,7 @@
         <v>578</v>
       </c>
       <c r="C170" s="4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>777</v>
@@ -6091,7 +6091,7 @@
         <v>600</v>
       </c>
       <c r="C192" s="4">
-        <v>300</v>
+        <v>1300</v>
       </c>
       <c r="D192" s="3">
         <v>3</v>
@@ -6159,7 +6159,7 @@
         <v>172</v>
       </c>
       <c r="C196" s="4">
-        <v>318</v>
+        <v>2318</v>
       </c>
       <c r="D196" s="3">
         <v>4</v>
@@ -6244,7 +6244,7 @@
         <v>176</v>
       </c>
       <c r="C201" s="6">
-        <v>202</v>
+        <v>1202</v>
       </c>
       <c r="D201" s="5">
         <v>5</v>
@@ -6737,7 +6737,7 @@
         <v>204</v>
       </c>
       <c r="C230" s="4">
-        <v>262</v>
+        <v>1262</v>
       </c>
       <c r="D230" s="3">
         <v>2</v>
@@ -7281,7 +7281,7 @@
         <v>232</v>
       </c>
       <c r="C262" s="4">
-        <v>279</v>
+        <v>1279</v>
       </c>
       <c r="D262" s="3">
         <v>6</v>
@@ -7604,7 +7604,7 @@
         <v>252</v>
       </c>
       <c r="C281" s="6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D281" s="5">
         <v>6</v>
@@ -7791,7 +7791,7 @@
         <v>704</v>
       </c>
       <c r="C292" s="4">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="D292" s="3" t="s">
         <v>777</v>
@@ -7825,7 +7825,7 @@
         <v>262</v>
       </c>
       <c r="C294" s="4">
-        <v>419</v>
+        <v>2419</v>
       </c>
       <c r="D294" s="3">
         <v>3</v>
@@ -8131,7 +8131,7 @@
         <v>286</v>
       </c>
       <c r="C312" s="4">
-        <v>607</v>
+        <v>1607</v>
       </c>
       <c r="D312" s="3">
         <v>5</v>
@@ -8216,7 +8216,7 @@
         <v>292</v>
       </c>
       <c r="C317" s="6">
-        <v>302</v>
+        <v>1302</v>
       </c>
       <c r="D317" s="5">
         <v>6</v>
@@ -8250,7 +8250,7 @@
         <v>296</v>
       </c>
       <c r="C319" s="6">
-        <v>315</v>
+        <v>1315</v>
       </c>
       <c r="D319" s="5">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53AAF42-5F9E-450C-B860-F6065E1FF9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77A4AD6-A68E-4336-B0B7-1B15AB91FF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4935,7 +4935,7 @@
         <v>522</v>
       </c>
       <c r="C124" s="4">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>777</v>
